--- a/file/SK이노베이션.xlsx
+++ b/file/SK이노베이션.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\0. JupyterNotebook\Finance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\my-web\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7960D67C-ECF6-42DF-A42D-8706B1F5095C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AC1F18-A83E-43B1-A1BE-015C13C4AA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="16395" xr2:uid="{574589F6-5CF4-430A-9C77-3C46C2002903}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{574589F6-5CF4-430A-9C77-3C46C2002903}"/>
   </bookViews>
   <sheets>
     <sheet name="SK이노베이션" sheetId="1" r:id="rId1"/>
@@ -1265,8 +1265,7 @@
         <v>-950.50000000000227</v>
       </c>
       <c r="F6" s="3">
-        <f>E6*100000000/B6*10</f>
-        <v>-8442.6756799565101</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.6">
@@ -1287,8 +1286,7 @@
         <v>-36211.5</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" ref="F7:F25" si="1">E7*100000000/B7*10</f>
-        <v>-321643.29340846336</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.6">
@@ -1309,8 +1307,7 @@
         <v>-34867.600000000006</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="1"/>
-        <v>-309706.30040868063</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.6">
@@ -1331,8 +1328,7 @@
         <v>-22978.6</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="1"/>
-        <v>-204104.01618037681</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.6">
@@ -1353,8 +1349,7 @@
         <v>-23304</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="1"/>
-        <v>-206994.33355676592</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.6">
@@ -1375,8 +1370,7 @@
         <v>-28077</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" si="1"/>
-        <v>-249389.80017479046</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.6">
@@ -1397,8 +1391,7 @@
         <v>-28629</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="1"/>
-        <v>-254292.85853916287</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.6">
@@ -1419,8 +1412,7 @@
         <v>-19651</v>
       </c>
       <c r="F13" s="3">
-        <f t="shared" si="1"/>
-        <v>-174547.10130123614</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.6">
@@ -1441,8 +1433,7 @@
         <v>-8372</v>
       </c>
       <c r="F14" s="3">
-        <f t="shared" si="1"/>
-        <v>-74363.051859648316</v>
+        <v>55727.877134189388</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.6">
@@ -1463,7 +1454,7 @@
         <v>6274</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F6:F25" si="1">E15*100000000/B15*10</f>
         <v>55727.877134189388</v>
       </c>
     </row>
@@ -1529,8 +1520,7 @@
         <v>-7062</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="1"/>
-        <v>-62727.170596373195</v>
+        <v>38798.114013729559</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.6">
@@ -1551,8 +1541,7 @@
         <v>-8404</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="1"/>
-        <v>-74647.287127148171</v>
+        <v>38798.114013729559</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.6">
